--- a/assets/docs/lop3/Cong nghe - Lop 3.xlsx
+++ b/assets/docs/lop3/Cong nghe - Lop 3.xlsx
@@ -1193,7 +1193,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở hoạt động Mở đầu bài “Dụng cụ và vật liệu làm thủ công”, GV chiếu ảnh chụp gần kéo, bút chì.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Mở đầu bài “Dụng cụ và vật liệu làm thủ công”, GV chiếu ảnh chụp gần kéo, bút chì, thước, hồ dán, giấy màu
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác nối dụng cụ với công việc: HS kéo kéo về ô cắt, hồ về ô dán
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -1254,7 +1255,8 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng, dừng hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khởi động bài “Làm đồ dùng học tập”, GV chiếu video hướng dẫn làm một đồ dùng học tập đơn giản, cho chạy chậm và dừng ở từng bước gấp, cắt
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng, dừng hình để cả lớp nhìn kĩ
 STEM: Sáng tạo đồ dùng học tập (Công nghệ – Mĩ thuật) — dạy thay cho tiết này.
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
@@ -1467,7 +1469,8 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khởi động bài “Làm đồ chơi”, GV chiếu video hướng dẫn làm một món đồ chơi đơn giản, cho chạy chậm và dừng ở từng bước gấp, cắt, dán
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Thực hành, GV chiếu lại đúng bước mà nhiều bạn còn lúng túng và dừng hình; HS đối chiếu sản phẩm của mình với hình trên màn hình để tìm ra…
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
